--- a/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -880,30 +881,35 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -928,22 +934,27 @@
           <t>Villavicencio Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -968,22 +979,27 @@
           <t>Zirakpur Area</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1008,22 +1024,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1048,22 +1069,27 @@
           <t>Manzanillo</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1088,22 +1114,27 @@
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1128,22 +1159,27 @@
           <t>Bogotá Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1168,22 +1204,27 @@
           <t>Montería Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1208,22 +1249,27 @@
           <t>Yopal Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1248,22 +1294,27 @@
           <t>Yopal Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1288,22 +1339,27 @@
           <t>Saltillo</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1328,22 +1384,27 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1368,22 +1429,27 @@
           <t>Cayo Santa María Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0</v>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1408,22 +1474,27 @@
           <t>Quito Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1448,22 +1519,27 @@
           <t>Carbondale Area</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1488,22 +1564,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.09420289855072464</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1528,22 +1609,27 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.1024390243902439</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1568,22 +1654,27 @@
           <t>Grande Prairie Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1608,22 +1699,27 @@
           <t>Guanacaste Area</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="13" t="n">
-        <v>0.1428571428571428</v>
+      <c r="H23" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="13" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1648,22 +1744,27 @@
           <t>Corbin Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1688,22 +1789,27 @@
           <t>Ohio</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1728,22 +1834,27 @@
           <t>Chihuahua</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="13" t="n">
-        <v>0.2</v>
+      <c r="H26" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I26" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1768,22 +1879,27 @@
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1808,22 +1924,27 @@
           <t>Belem Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="13" t="n">
-        <v>0.2</v>
+      <c r="H28" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="I28" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1848,22 +1969,27 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1888,22 +2014,27 @@
           <t>Hermosillo</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1928,22 +2059,27 @@
           <t>Tegucigalpa Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="13" t="n">
-        <v>0.25</v>
+      <c r="H31" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I31" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J31" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1968,22 +2104,27 @@
           <t>Hot Springs Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.25</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2008,22 +2149,27 @@
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.2775</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>0.1025</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2048,22 +2194,27 @@
           <t>Puerto Plata</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.282051282051282</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2088,22 +2239,27 @@
           <t>La Crosse Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.2941176470588235</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2128,22 +2284,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.3125</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2168,22 +2329,27 @@
           <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.3142857142857143</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2208,22 +2374,27 @@
           <t>Santiago de Chile Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.3174603174603174</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>0.06349206349206349</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2248,22 +2419,27 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.3181818181818182</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2288,22 +2464,27 @@
           <t>Morehead Area</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.32</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>0.08</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2328,22 +2509,27 @@
           <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.3272727272727273</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2368,22 +2554,27 @@
           <t>Chihuahua</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="I42" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2408,22 +2599,27 @@
           <t>Kingsville Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="13" t="n">
-        <v>0.3333333333333333</v>
+      <c r="H43" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2448,22 +2644,27 @@
           <t>Timmins Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="13" t="n">
-        <v>0.3333333333333333</v>
+      <c r="H44" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I44" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2488,22 +2689,27 @@
           <t>Apulia Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="13" t="n">
-        <v>0.3333333333333333</v>
+      <c r="H45" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="J45" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2528,22 +2734,27 @@
           <t>Northwest Indiana Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="13" t="n">
-        <v>0.3333333333333333</v>
+      <c r="H46" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="I46" s="13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2568,22 +2779,27 @@
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.3414634146341464</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2608,22 +2824,27 @@
           <t>Jacksonville Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2648,22 +2869,27 @@
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.3742138364779874</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>0.03459119496855346</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2688,22 +2914,27 @@
           <t>Traverse City Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.375</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>0.0625</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2728,22 +2959,27 @@
           <t>Fife Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.375</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2768,22 +3004,27 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.3863636363636364</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2808,22 +3049,27 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>456</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.4078947368421053</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2848,22 +3094,27 @@
           <t>Berea Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.4117647058823529</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2888,22 +3139,27 @@
           <t>Monterrey</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.4230769230769231</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2920,18 +3176,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2951,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2978,25 +3235,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -3021,19 +3283,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>9002</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.9984447900466563</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.000555432126194179</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3058,19 +3325,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>3930</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9692111959287532</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.004071246819338422</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3095,19 +3367,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>2372</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.9978920741989882</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.003372681281618887</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3132,19 +3409,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>2223</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9986504723346828</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.001799370220422852</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3169,19 +3451,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>1971</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.0005073566717402334</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3206,19 +3493,24 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>1528</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9823298429319371</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.00130890052356021</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3243,19 +3535,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>1487</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9858776059179556</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.002689979825151311</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3280,19 +3577,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>1478</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.9912043301759134</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.005412719891745603</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3317,19 +3619,24 @@
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>1351</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9452257586972613</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.009622501850481125</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3354,19 +3661,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>1147</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9755884917175239</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.006102877070619006</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3391,19 +3703,24 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>1140</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.8210526315789474</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.009649122807017544</v>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3428,19 +3745,24 @@
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>1099</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9845313921747043</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.01455868971792539</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3465,19 +3787,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.994475138121547</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.005524861878453038</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3502,19 +3829,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>1016</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9744094488188977</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.002952755905511811</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3539,19 +3871,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>989</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9757330637007078</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.002022244691607685</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3576,19 +3913,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>936</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9861111111111112</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.001068376068376068</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3613,19 +3955,24 @@
           <t>Madrid</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9768722466960352</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.004405286343612335</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3650,19 +3997,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>895</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.823463687150838</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.004469273743016759</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3687,19 +4039,24 @@
           <t>San Diego</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>881</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.8047673098751419</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.00681044267877412</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3724,19 +4081,24 @@
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>870</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9977011494252873</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.005747126436781609</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3761,19 +4123,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>847</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9693034238488784</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.003541912632821724</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3798,19 +4165,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9716312056737588</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.00591016548463357</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3835,19 +4207,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>814</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.8808353808353808</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3872,19 +4249,24 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>808</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9900990099009901</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002475247524752475</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3909,19 +4291,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>792</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9633838383838383</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.001262626262626263</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3946,19 +4333,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>784</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.8966836734693877</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.007653061224489796</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3983,19 +4375,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>777</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9884169884169884</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.01158301158301158</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4020,19 +4417,24 @@
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>691</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9971056439942113</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.01447178002894356</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4057,19 +4459,24 @@
           <t>Jakarta Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>683</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.9546120058565154</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.008784773060029283</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4094,19 +4501,24 @@
           <t>Barcelona Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>653</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9540581929555896</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.003062787136294028</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4131,19 +4543,24 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>646</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9086687306501547</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.0108359133126935</v>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4168,19 +4585,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>640</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.865625</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.00625</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4205,19 +4627,24 @@
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>621</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.7681159420289855</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.01127214170692432</v>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4242,19 +4669,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9983739837398374</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.003252032520325203</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4279,19 +4711,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>607</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9686985172981878</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.01482701812191104</v>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4316,19 +4753,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9965576592082617</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.001721170395869191</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4353,19 +4795,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>572</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9790209790209791</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.006993006993006993</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4390,19 +4837,24 @@
           <t>SinClasificar</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>557</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.6642728904847397</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.01077199281867145</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4427,19 +4879,24 @@
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>542</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.992619926199262</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.005535055350553505</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4464,19 +4921,24 @@
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>511</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9960861056751468</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.005870841487279843</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4501,19 +4963,24 @@
           <t>Hamburg Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.964</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4538,19 +5005,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>496</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.9939516129032258</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.008064516129032258</v>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4575,19 +5047,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>469</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.004264392324093817</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4612,19 +5089,24 @@
           <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>458</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9934497816593887</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.002183406113537118</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4649,19 +5131,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>451</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9645232815964523</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.002217294900221729</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4686,19 +5173,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9575892857142857</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.01339285714285714</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4723,19 +5215,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4760,19 +5257,24 @@
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.7726218097447796</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.009280742459396751</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4797,19 +5299,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>425</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9905882352941177</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.009411764705882352</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4834,19 +5341,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.002369668246445498</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4863,18 +5375,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4894,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4921,25 +5434,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -4964,19 +5482,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
         <v>907</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="n">
         <v>0.07497243660418963</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5001,19 +5524,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>635</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>626</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="n">
         <v>0.9858267716535433</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5038,19 +5566,24 @@
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>551</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>535</v>
       </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="n">
         <v>0.9709618874773139</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5075,19 +5608,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>428</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>0.8183556405353728</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5112,19 +5650,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>511</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="n">
         <v>0.9295499021526419</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5149,19 +5692,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>487</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="n">
         <v>0.9815195071868583</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5186,19 +5734,24 @@
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>449</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="n">
         <v>0.9599109131403119</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5223,19 +5776,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>430</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>426</v>
       </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
         <v>0.9906976744186047</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5260,19 +5818,24 @@
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>421</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
+      <c r="H14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="n">
         <v>0.9904988123515439</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5297,19 +5860,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>397</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>384</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
         <v>0.9672544080604534</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5334,19 +5902,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>394</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13" t="n">
         <v>0.8451776649746193</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5371,19 +5944,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>0.9921259842519685</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5408,19 +5986,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>369</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="H18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5445,19 +6028,24 @@
           <t>Milan</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>356</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13" t="n">
         <v>0.9775280898876404</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5482,19 +6070,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>341</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5519,19 +6112,24 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>337</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13" t="n">
         <v>0.9970414201183432</v>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5556,19 +6154,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>336</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="13" t="n">
+      <c r="H22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13" t="n">
         <v>0.9880952380952381</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5593,19 +6196,24 @@
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>329</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5630,19 +6238,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>319</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13" t="n">
+      <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13" t="n">
         <v>0.9937694704049844</v>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5667,19 +6280,24 @@
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>319</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5704,19 +6322,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>313</v>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F26" s="12" t="n">
         <v>313</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13" t="n">
+        <v>313</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5741,19 +6364,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13" t="n">
         <v>0.9867549668874173</v>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5778,19 +6406,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>296</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13" t="n">
         <v>0.9932885906040269</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5815,19 +6448,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13" t="n">
         <v>0.9828767123287672</v>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5852,19 +6490,24 @@
           <t>Londres</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13" t="n">
+      <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13" t="n">
         <v>0.9791666666666666</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5889,19 +6532,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="13" t="n">
         <v>0.9965277777777778</v>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5926,19 +6574,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="13" t="n">
+      <c r="H32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="13" t="n">
         <v>0.7383512544802867</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5963,19 +6616,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>274</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="G33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="13" t="n">
         <v>0.8905109489051095</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6000,19 +6658,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
-        <v>274</v>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F34" s="12" t="n">
         <v>274</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="13" t="n">
+        <v>274</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6037,19 +6700,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>272</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13" t="n">
         <v>0.5367647058823529</v>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6074,19 +6742,24 @@
           <t>Kanazawa Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13" t="n">
         <v>0.9962962962962963</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6111,19 +6784,24 @@
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13" t="n">
         <v>0.9702602230483272</v>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6148,19 +6826,24 @@
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="13" t="n">
+      <c r="H38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13" t="n">
         <v>0.9888475836431226</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6185,19 +6868,24 @@
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>253</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13" t="n">
         <v>0.8102766798418972</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6222,19 +6910,24 @@
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>251</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13" t="n">
         <v>0.996031746031746</v>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6259,19 +6952,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13" t="n">
         <v>0.5952380952380952</v>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6296,19 +6994,24 @@
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="13" t="n">
+      <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="13" t="n">
         <v>0.924</v>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6333,19 +7036,24 @@
           <t>Austin</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>216</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13" t="n">
         <v>0.8780487804878049</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6370,19 +7078,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="13" t="n">
+      <c r="H44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13" t="n">
         <v>0.8943089430894309</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6407,19 +7120,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="13" t="n">
+      <c r="H45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13" t="n">
         <v>0.9915611814345991</v>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6444,19 +7162,24 @@
           <t>Dallas</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>229</v>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F46" s="12" t="n">
         <v>229</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="13" t="n">
+        <v>229</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6481,19 +7204,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13" t="n">
+      <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13" t="n">
         <v>0.6517857142857143</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6518,19 +7246,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="13" t="n">
+      <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13" t="n">
         <v>0.9865470852017937</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6555,19 +7288,24 @@
           <t>Boston</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="13" t="n">
+      <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13" t="n">
         <v>0.9636363636363636</v>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6592,19 +7330,24 @@
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="G50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="13" t="n">
+      <c r="H50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13" t="n">
         <v>0.8136363636363636</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6629,19 +7372,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="13" t="n">
+      <c r="H51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13" t="n">
         <v>0.9907834101382489</v>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6666,19 +7414,24 @@
           <t>Adjara Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>214</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="13" t="n">
+      <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13" t="n">
         <v>0.9018691588785047</v>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6703,19 +7456,24 @@
           <t>Abu Dhabi</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>211</v>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F53" s="12" t="n">
         <v>211</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="13" t="n">
+        <v>211</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6740,19 +7498,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>191</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="13" t="n">
+      <c r="H54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13" t="n">
         <v>0.9271844660194175</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6777,19 +7540,24 @@
           <t>London Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="G55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="13" t="n">
+      <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13" t="n">
         <v>0.9754901960784313</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6837,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +11291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10970,18 +11738,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11001,7 +11770,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 03:47 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11028,25 +11797,30 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -11071,19 +11845,24 @@
           <t>Montería Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11108,19 +11887,24 @@
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11145,19 +11929,24 @@
           <t>Bogotá Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11182,19 +11971,24 @@
           <t>Cayo Santa María Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11219,19 +12013,24 @@
           <t>Quito Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11256,19 +12055,24 @@
           <t>Saltillo</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11293,19 +12097,24 @@
           <t>Carbondale Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11330,19 +12139,24 @@
           <t>Zirakpur Area</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11367,19 +12181,24 @@
           <t>Medellin Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>0</v>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11404,19 +12223,24 @@
           <t>Yopal Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11441,19 +12265,24 @@
           <t>Villavicencio Area</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11478,19 +12307,24 @@
           <t>Manzanillo</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>0</v>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11515,19 +12349,24 @@
           <t>Yopal Area</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11552,19 +12391,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>0</v>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11589,19 +12433,24 @@
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>1971</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.0005073566717402334</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11626,19 +12475,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>9002</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9984447900466563</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.000555432126194179</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11663,19 +12517,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>936</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9861111111111112</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.001068376068376068</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11700,19 +12559,24 @@
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>792</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9633838383838383</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.001262626262626263</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11737,19 +12601,24 @@
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>1528</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.9823298429319371</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.00130890052356021</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11774,19 +12643,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9965576592082617</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.001721170395869191</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11811,19 +12685,24 @@
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>2223</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9986504723346828</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.001799370220422852</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11848,19 +12727,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>989</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9757330637007078</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.002022244691607685</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11885,19 +12769,24 @@
           <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
         <v>458</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.9934497816593887</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002183406113537118</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11922,19 +12811,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
         <v>451</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9645232815964523</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002217294900221729</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11959,19 +12853,24 @@
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.002369668246445498</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11996,19 +12895,24 @@
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.1024390243902439</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12033,19 +12937,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.8951219512195122</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12070,19 +12979,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>814</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.8808353808353808</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12107,19 +13021,24 @@
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>808</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.9900990099009901</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.002475247524752475</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12144,19 +13063,24 @@
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>403</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9578163771712159</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.002481389578163772</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12181,19 +13105,24 @@
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>1487</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9858776059179556</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.002689979825151311</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12218,19 +13147,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>367</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9754768392370572</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.002724795640326975</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12255,19 +13189,24 @@
           <t>New York</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>359</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.9805013927576601</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.002785515320334262</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12292,19 +13231,24 @@
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>352</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.6960227272727273</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.002840909090909091</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12329,19 +13273,24 @@
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>1016</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9744094488188977</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.002952755905511811</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12366,19 +13315,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>335</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.002985074626865672</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12403,19 +13357,24 @@
           <t>Greater Glasgow Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>329</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.7264437689969605</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.00303951367781155</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12440,19 +13399,24 @@
           <t>Barcelona Area</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>653</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9540581929555896</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.003062787136294028</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12477,19 +13441,24 @@
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.8070739549839229</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.003215434083601286</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12514,19 +13483,24 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9983739837398374</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.003252032520325203</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12551,19 +13525,24 @@
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>2372</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.9978920741989882</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.003372681281618887</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12588,19 +13567,24 @@
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>294</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.9897959183673469</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.003401360544217687</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12625,19 +13609,24 @@
           <t>Brunswick Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.8961937716262975</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.003460207612456748</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12662,19 +13651,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>847</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9693034238488784</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.003541912632821724</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12699,19 +13693,24 @@
           <t>Berlin Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9740740740740741</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.003703703703703704</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12736,19 +13735,24 @@
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9922480620155039</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.003875968992248062</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12773,19 +13777,24 @@
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.003937007874015748</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12810,19 +13819,24 @@
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.9603174603174603</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.003968253968253968</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12847,19 +13861,24 @@
           <t>Sharm el Sheikh Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.004032258064516129</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12884,19 +13903,24 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>247</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9190283400809717</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.004048582995951417</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8649,11 +8649,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -8680,7 +8680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9076,6 +9076,1406 @@
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>5638</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>5365</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.951578573962398</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.01986520042568287</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>5562</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>5375</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9663790003595829</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.01330456670262496</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>5374</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>5219</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9711574246371418</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.002419054707852624</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>5090</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>4895</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.9616895874263262</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.01630648330058939</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>4839</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9506096300888613</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.006612936557139905</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>4671</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>4569</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.9781631342324983</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.01605651894669236</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>4422</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>4155</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9396200814111262</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.04681139755766622</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Edinburgh Area</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>4376</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>4016</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9177330895795247</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.01256855575868373</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>4351</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>4089</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9397839577108711</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.02505171225005746</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>4351</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>4218</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9694323144104804</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.01907607446564008</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>4253</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>3913</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9200564307547613</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.002116153303550435</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>4242</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>3531</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.8323903818953324</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.05445544554455446</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>4086</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>3837</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.9390602055800293</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.001223690651003426</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>3954</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>3812</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9640870005058169</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.02276176024279211</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>3496</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.908051948051948</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.01896103896103896</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>3796</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>3181</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.8379873551106428</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.01422550052687039</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>3669</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9555737258108477</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.02098664486236032</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>3545</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>3385</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.9548660084626234</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.01777150916784203</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Osaka Area</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>3499</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>3049</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.8713918262360675</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.01543298085167191</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>3383</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>3149</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9308306237067692</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.02335205438959503</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>3362</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>3243</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.9646044021415824</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.01457465794170137</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Múnich Area</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>3098</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>2753</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.8886378308586185</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.01484828921885087</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>3062</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>2908</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9497060744611365</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.003265839320705421</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>2890</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>2814</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9737024221453288</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.00657439446366782</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Ixtapa / Zihuatanejo</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>2533</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.8795138888888889</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Berlin Area</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>2761</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>2588</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9373415429192321</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.01412531691416154</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>2736</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>2644</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.966374269005848</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.0135233918128655</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>2733</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>2619</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9582875960482986</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.01866081229418222</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>2650</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>2561</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.9664150943396227</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.0569811320754717</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>2590</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.9652509652509652</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.02432432432432433</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>2587</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>2277</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.8801700811751063</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.02473908001546192</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>2443</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.963978714695047</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.0122799836266885</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>2341</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>2222</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9491670226398975</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.02563007261853908</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>2232</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>2187</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.9798387096774194</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.008512544802867384</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Manchester Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>2224</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.01888489208633094</v>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>London Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9429622815087396</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.009659613615455382</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Vienna Area</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>2079</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9591149591149591</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.01346801346801347</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.9515396264512872</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.03685007571933367</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9306476287608363</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.03008669046404895</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Los Cabos Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.8929532006455083</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0.04679935449166218</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9123,7 +10523,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9599,7 +10999,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -821,19 +821,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -875,35 +876,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -925,25 +931,30 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.09420289855072464</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="J6" s="13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -965,25 +976,30 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.1024390243902439</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="J7" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1005,25 +1021,30 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Grande Prairie Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="J8" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1045,25 +1066,30 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="J9" s="13" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1085,25 +1111,30 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.2</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="J10" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1125,25 +1156,30 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.2775</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.1025</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1165,25 +1201,30 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Puerto Plata</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.282051282051282</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="J12" s="13" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1205,25 +1246,30 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.3125</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>0.02083333333333333</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1245,25 +1291,30 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.3142857142857143</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1285,25 +1336,30 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Santiago de Chile Area</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.3174603174603174</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="J15" s="13" t="n">
         <v>0.06349206349206349</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1325,25 +1381,30 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.3181818181818182</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="J16" s="13" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1365,25 +1426,30 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Morehead Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.32</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>0.08</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1405,25 +1471,30 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.3272727272727273</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="J18" s="13" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1445,25 +1516,30 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.3414634146341464</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="J19" s="13" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1485,25 +1561,30 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.3742138364779874</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>0.03459119496855346</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1525,25 +1606,30 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>Fife Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.375</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1565,25 +1651,30 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Traverse City Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.375</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>0.0625</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1605,25 +1696,30 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Mexico City - Central Mexico</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.3863636363636364</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1645,25 +1741,30 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>456</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.4078947368421053</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1685,25 +1786,30 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Monterrey</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.4230769230769231</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1725,25 +1831,30 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Riviera Nayarit</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>501</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>216</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.4311377245508982</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>0.01596806387225549</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1765,25 +1876,30 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.4342105263157895</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>0.0131578947368421</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1805,25 +1921,30 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Gunnison - Crested Butte Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.4385964912280702</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="J28" s="13" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1845,25 +1966,30 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.4464285714285715</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1885,25 +2011,30 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.4482758620689655</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1925,25 +2056,30 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Key Largo Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.4585635359116022</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="J31" s="13" t="n">
         <v>0.01104972375690608</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -1965,25 +2101,30 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Manchester Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.4660194174757282</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>0.03883495145631068</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2005,25 +2146,30 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2045,25 +2191,30 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.4897959183673469</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>0.06122448979591837</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2085,25 +2236,30 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.4952830188679245</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>0.01415094339622642</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2125,25 +2281,30 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Phoenix (and vicinity), AZ, US</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2165,25 +2326,30 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>San Diego Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.5119047619047619</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2205,25 +2371,30 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>São Paulo</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>0.1304347826086956</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2245,25 +2416,30 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>HotelBeds Apitude</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.525</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>0.025</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2285,25 +2461,30 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.5286343612334802</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>0.00881057268722467</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2325,25 +2506,30 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>0.02941176470588235</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2365,25 +2551,30 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Sedona Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.5370370370370371</v>
       </c>
-      <c r="I42" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2405,25 +2596,30 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="J43" s="13" t="n">
         <v>0.006993006993006993</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2445,25 +2641,30 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Paducah Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="I44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2485,25 +2686,30 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>597</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>329</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.5510887772194305</v>
       </c>
-      <c r="I45" s="13" t="n">
+      <c r="J45" s="13" t="n">
         <v>0.02010050251256281</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2525,25 +2731,30 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.5526315789473685</v>
       </c>
-      <c r="I46" s="13" t="n">
+      <c r="J46" s="13" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2565,25 +2776,30 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Devon Area</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2605,25 +2821,30 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2645,25 +2866,30 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Newcastle Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.5662650602409639</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>0.01204819277108434</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2685,25 +2911,30 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Melbourne Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.5662650602409639</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>0.02409638554216868</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2725,25 +2956,30 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Boone Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2765,25 +3001,30 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Ishigaki Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>157</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.5668789808917197</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>0.006369426751592357</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2805,25 +3046,30 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Crystal River Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.5686274509803921</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>0.09803921568627451</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2845,25 +3091,30 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.5704225352112676</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>0.01408450704225352</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2885,25 +3136,30 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Nashville (and vicinity), TN, US</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -2920,18 +3176,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2951,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2973,30 +3230,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -3018,22 +3280,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>9002</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.9984447900466563</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.000555432126194179</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3055,22 +3322,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>3930</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9692111959287532</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.004071246819338422</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3092,22 +3364,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>2372</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.9978920741989882</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.003372681281618887</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3129,22 +3406,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>2223</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9986504723346828</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.001799370220422852</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3166,22 +3448,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>1971</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.0005073566717402334</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3203,22 +3490,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1528</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9823298429319371</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.00130890052356021</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3240,22 +3532,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>1487</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9858776059179556</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.002689979825151311</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3277,22 +3574,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>1478</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.9912043301759134</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.005412719891745603</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3314,22 +3616,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Halifax Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>1351</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9452257586972613</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.009622501850481125</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3351,22 +3658,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>1147</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9755884917175239</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.006102877070619006</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3388,22 +3700,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>1140</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0.8210526315789474</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.009649122807017544</v>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3425,22 +3742,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>1099</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.9845313921747043</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.01455868971792539</v>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -3462,22 +3784,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>1086</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.994475138121547</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.005524861878453038</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3499,22 +3826,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>1016</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.9744094488188977</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.002952755905511811</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3536,22 +3868,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>989</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9757330637007078</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.002022244691607685</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3573,22 +3910,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>936</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9861111111111112</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.001068376068376068</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3610,22 +3952,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9768722466960352</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.004405286343612335</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3647,22 +3994,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>895</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.823463687150838</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.004469273743016759</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3684,22 +4036,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>881</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.8047673098751419</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.00681044267877412</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3721,22 +4078,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Honolulu Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>870</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.9977011494252873</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.005747126436781609</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3758,22 +4120,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>847</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9693034238488784</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.003541912632821724</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3795,22 +4162,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>846</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>0.9716312056737588</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.00591016548463357</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3832,22 +4204,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>814</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.8808353808353808</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3869,22 +4246,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>808</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9900990099009901</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.002475247524752475</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3906,22 +4288,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>792</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.9633838383838383</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.001262626262626263</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3943,22 +4330,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>784</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.8966836734693877</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.007653061224489796</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -3980,22 +4372,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>777</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9884169884169884</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.01158301158301158</v>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4017,22 +4414,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Niagara Falls, Canada</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>691</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9971056439942113</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.01447178002894356</v>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4054,22 +4456,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Jakarta Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>683</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.9546120058565154</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.008784773060029283</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4091,22 +4498,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Barcelona Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>653</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9540581929555896</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.003062787136294028</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4128,22 +4540,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>646</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9086687306501547</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.0108359133126935</v>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4165,22 +4582,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>640</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.865625</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.00625</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4202,22 +4624,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>621</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>0.7681159420289855</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.01127214170692432</v>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4239,22 +4666,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9983739837398374</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.003252032520325203</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4276,22 +4708,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>607</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>0.9686985172981878</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.01482701812191104</v>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4313,22 +4750,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9965576592082617</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.001721170395869191</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4350,22 +4792,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>572</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.9790209790209791</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.006993006993006993</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4387,22 +4834,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>SinClasificar</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>557</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.6642728904847397</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.01077199281867145</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4424,22 +4876,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>542</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>0.992619926199262</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.005535055350553505</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4461,22 +4918,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Osaka Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>511</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9960861056751468</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.005870841487279843</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4498,22 +4960,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Hamburg Area</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.964</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4535,22 +5002,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>496</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.9939516129032258</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.008064516129032258</v>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4572,22 +5044,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>469</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.004264392324093817</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4609,22 +5086,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>458</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9934497816593887</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.002183406113537118</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4646,22 +5128,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>451</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9645232815964523</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.002217294900221729</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4683,22 +5170,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>448</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.9575892857142857</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.01339285714285714</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4720,22 +5212,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4757,22 +5254,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Tbilisi Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.7726218097447796</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.009280742459396751</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4794,22 +5296,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>425</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>0.9905882352941177</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.009411764705882352</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -4831,22 +5338,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.002369668246445498</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -4863,18 +5375,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4894,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4916,30 +5429,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
@@ -4961,22 +5479,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>907</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.07497243660418963</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -4998,22 +5521,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>635</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>626</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.9858267716535433</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5035,22 +5563,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>551</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>535</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.9709618874773139</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5072,22 +5605,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>428</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.8183556405353728</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5109,22 +5647,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>511</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.9295499021526419</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -5146,22 +5689,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>487</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.9815195071868583</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5183,22 +5731,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Miami Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>449</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.9599109131403119</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5220,22 +5773,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>430</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>426</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.9906976744186047</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5257,22 +5815,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>Antalya Area</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>421</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>417</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.9904988123515439</v>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5294,22 +5857,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>397</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>384</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.9672544080604534</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -5331,22 +5899,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>394</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.8451776649746193</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5368,22 +5941,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>381</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>378</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.9921259842519685</v>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5405,22 +5983,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>369</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5442,22 +6025,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>356</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.9775280898876404</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5479,22 +6067,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>341</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5516,22 +6109,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>337</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.9970414201183432</v>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5553,22 +6151,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>336</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>332</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.9880952380952381</v>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5590,22 +6193,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>329</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5627,22 +6235,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>319</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.9937694704049844</v>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5664,22 +6277,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>319</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -5701,22 +6319,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>313</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>313</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5738,22 +6361,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.9867549668874173</v>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5775,22 +6403,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>296</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.9932885906040269</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5812,22 +6445,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.9828767123287672</v>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5849,22 +6487,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.9791666666666666</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5886,22 +6529,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>288</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.9965277777777778</v>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5923,22 +6571,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.7383512544802867</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -5960,22 +6613,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>274</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>274</v>
       </c>
       <c r="G33" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -5997,22 +6655,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>274</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.8905109489051095</v>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6034,22 +6697,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>272</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.5367647058823529</v>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6071,22 +6739,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Kanazawa Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.9962962962962963</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6108,22 +6781,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Greenville Area</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.9888475836431226</v>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6145,22 +6823,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.9702602230483272</v>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6182,22 +6865,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Punta Cana</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>253</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.8102766798418972</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6219,22 +6907,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.5952380952380952</v>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
@@ -6256,22 +6949,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>251</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.996031746031746</v>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6293,22 +6991,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Atlanta Area</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.924</v>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6330,22 +7033,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>216</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.8780487804878049</v>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6367,22 +7075,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.8943089430894309</v>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6404,22 +7117,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.9915611814345991</v>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6441,22 +7159,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Dallas</t>
         </is>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>229</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>229</v>
       </c>
       <c r="G46" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6478,22 +7201,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.6517857142857143</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6515,22 +7243,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.9865470852017937</v>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6552,22 +7285,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.9636363636363636</v>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6589,22 +7327,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Edinburgh Area</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.8136363636363636</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6626,22 +7369,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>215</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.9907834101382489</v>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6663,22 +7411,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Adjara Area</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>214</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.9018691588785047</v>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6700,22 +7453,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Abu Dhabi</t>
         </is>
-      </c>
-      <c r="E53" s="12" t="n">
-        <v>211</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>211</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6737,22 +7495,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>191</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.9271844660194175</v>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6774,22 +7537,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>London Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.9754901960784313</v>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6837,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8680,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10492,18 +11260,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10523,7 +11292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10535,40 +11304,45 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ExternalProviderName</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -10583,27 +11357,32 @@
           <t>DerbySoft</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>358102</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>335695</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>8030</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.937428442175693</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.02242377869992349</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10618,27 +11397,32 @@
           <t>Internal</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>51130</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>48466</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>2085</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9478975161353412</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.04077840797965969</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10653,27 +11437,32 @@
           <t>Expedia</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>28520</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>27112</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9506311360448808</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.003260869565217391</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10688,27 +11477,32 @@
           <t>HBSI</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>16973</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>13562</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>624</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.7990337595003829</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.03676427266835562</v>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10723,27 +11517,32 @@
           <t>SynXis</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>7663</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>7579</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>383</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9890382356779329</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.04998042542085345</v>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10758,27 +11557,32 @@
           <t>HotelBeds Apitude</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>5393</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>4860</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.9011681809753384</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.009827554236973854</v>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10793,27 +11597,32 @@
           <t>Siteminder</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>4561</v>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>4561</v>
       </c>
       <c r="E12" s="12" t="n">
+        <v>4561</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>214</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.04691953518965139</v>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10828,27 +11637,32 @@
           <t>Travelclick</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>614</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D13" s="12" t="n">
         <v>614</v>
       </c>
       <c r="E13" s="12" t="n">
+        <v>614</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.05374592833876222</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10863,27 +11677,32 @@
           <t>Omnibees</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>202</v>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Producto Propio</t>
+        </is>
       </c>
       <c r="D14" s="12" t="n">
         <v>202</v>
       </c>
       <c r="E14" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10898,27 +11717,32 @@
           <t>Hotel Unico V2</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>26</v>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
       </c>
       <c r="D15" s="12" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10933,25 +11757,30 @@
           <t>Travelgate</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>0</v>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Third Party</t>
+        </is>
       </c>
       <c r="D16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="n">
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -10968,18 +11797,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10999,7 +11829,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11021,30 +11851,35 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Destino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -11066,22 +11901,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>1971</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>0.0005073566717402334</v>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11103,22 +11943,27 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>9002</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.9984447900466563</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>0.000555432126194179</v>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11140,22 +11985,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>936</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.9861111111111112</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>0.001068376068376068</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11177,22 +12027,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>792</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.9633838383838383</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>0.001262626262626263</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11214,22 +12069,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>1528</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.9823298429319371</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.00130890052356021</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11251,22 +12111,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.9965576592082617</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.001721170395869191</v>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11288,22 +12153,27 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
           <t>Istanbul Area</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>2223</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.9986504723346828</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>0.001799370220422852</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11325,22 +12195,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>989</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.9757330637007078</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>0.002022244691607685</v>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11362,22 +12237,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
           <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>458</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.9934497816593887</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.002183406113537118</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11399,22 +12279,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>451</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.9645232815964523</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.002217294900221729</v>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11436,22 +12321,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
           <t>Cancún</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.002369668246445498</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11473,22 +12363,27 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.8951219512195122</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11510,22 +12405,27 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.1024390243902439</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>0.002439024390243902</v>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11547,22 +12447,27 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>814</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.8808353808353808</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>0.002457002457002457</v>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11584,22 +12489,27 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
           <t>Anaheim Area</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>808</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.9900990099009901</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>0.002475247524752475</v>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11621,22 +12531,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
           <t>French Riviera Area</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>403</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.9578163771712159</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>0.002481389578163772</v>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11658,22 +12573,27 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
           <t>El Cairo Area</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>1487</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0.9858776059179556</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>0.002689979825151311</v>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11695,22 +12615,27 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>367</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.9754768392370572</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>0.002724795640326975</v>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11732,22 +12657,27 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>359</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.9805013927576601</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>0.002785515320334262</v>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11769,22 +12699,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>352</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.6960227272727273</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>0.002840909090909091</v>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11806,22 +12741,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
           <t>New Orleans</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>1016</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.9744094488188977</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>0.002952755905511811</v>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11843,22 +12783,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>335</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>0.002985074626865672</v>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11880,22 +12825,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
           <t>Greater Glasgow Area</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>329</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.7264437689969605</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>0.00303951367781155</v>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11917,22 +12867,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
           <t>Barcelona Area</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>653</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.9540581929555896</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>0.003062787136294028</v>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11954,22 +12909,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.8070739549839229</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>0.003215434083601286</v>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -11991,22 +12951,27 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>615</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>0.9983739837398374</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>0.003252032520325203</v>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12028,22 +12993,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
           <t>Riviera Maya</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>2372</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.9978920741989882</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>0.003372681281618887</v>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12065,22 +13035,27 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>294</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>0.9897959183673469</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>0.003401360544217687</v>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12102,22 +13077,27 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
           <t>Brunswick Area</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>0.8961937716262975</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>0.003460207612456748</v>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12139,22 +13119,27 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>847</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.9693034238488784</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>0.003541912632821724</v>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12176,22 +13161,27 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
           <t>Berlin Area</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>270</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>0.9740740740740741</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>0.003703703703703704</v>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12213,22 +13203,27 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>0.9922480620155039</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>0.003875968992248062</v>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12250,22 +13245,27 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
           <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>0.003937007874015748</v>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12287,22 +13287,27 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
           <t>Toronto Area</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>252</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.9603174603174603</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>0.003968253968253968</v>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12324,22 +13329,27 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
           <t>Sharm el Sheikh Area</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>0.004032258064516129</v>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12361,22 +13371,27 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>247</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>0.9190283400809717</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>0.004048582995951417</v>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12398,22 +13413,27 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>0.004065040650406504</v>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12435,22 +13455,27 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>3930</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0.9692111959287532</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>0.004071246819338422</v>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12472,22 +13497,27 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>Dubai Area</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>469</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>0.004264392324093817</v>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12509,22 +13539,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
           <t>Trois-Rivieres Area</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.9956140350877193</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>0.004385964912280702</v>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12546,22 +13581,27 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>908</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.9768722466960352</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>0.004405286343612335</v>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="J46" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12583,22 +13623,27 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>Londres</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>895</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>0.823463687150838</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>0.004469273743016759</v>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12620,22 +13665,27 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>222</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0.9504504504504504</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>0.004504504504504504</v>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12657,22 +13707,27 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
           <t>Huelva Area</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>218</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>0.9908256880733946</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>0.004587155963302753</v>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12694,22 +13749,27 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
           <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0.9631336405529954</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>0.004608294930875576</v>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12731,22 +13791,27 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>432</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>0.004629629629629629</v>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12768,22 +13833,27 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
           <t>Orlando</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>0.9712918660287081</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>0.004784688995215311</v>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12805,22 +13875,27 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
           <t>Cartagena Area</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>0.9951923076923077</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>0.004807692307692308</v>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12842,22 +13917,27 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
           <t>Rome Area</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>0.004830917874396135</v>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12879,22 +13959,27 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
           <t>Múnich Area</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>408</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>0.9852941176470589</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>0.004901960784313725</v>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_CUG_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
